--- a/partner_results/obi/ClassMissingGermanLabel_obi.xlsx
+++ b/partner_results/obi/ClassMissingGermanLabel_obi.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,7 +446,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>collection of specimens [obi]</t>
+          <t>processed material [obi]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -456,12 +456,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Person: Chris Stoeckert, Jie Zheng</t>
+          <t>PERSON: Alan Ruttenberg</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>A material entity that has two or more specimens as its parts.</t>
+          <t>Is a material entity that is created or changed during material processing.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -469,22 +469,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>k-nearest neighbors [obi]</t>
+          <t>protocol [obi]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>dataset creating</t>
+          <t>plan specification</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>James Malone</t>
+          <t>PlanAndPlannedProcess Branch</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>A k-nearest neighbors is a data transformation which achieves a class discovery or partitioning objective, in which an input data object with vector y is assigned to a class label based upon the k closest training data set points to y; where k is the largest value that class label is assigned.</t>
+          <t>A plan specification which has sufficient level of detail and quantitative information to communicate it between investigation agents, so that different investigation agents will reliably be able to independently reproduce the process.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -492,22 +492,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>manufacturing [obi]</t>
+          <t>collection of specimens [obi]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>material processing [obi]</t>
+          <t>material entity</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>PERSON: Melanie Courtot</t>
+          <t>Person: Chris Stoeckert, Jie Zheng</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Manufacturing is a process with the intent to produce a processed material which will have a function for future use. A person or organization (having manufacturer role) is a participant in this process</t>
+          <t>A material entity that has two or more specimens as its parts.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -515,22 +515,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>k-means clustering [obi]</t>
+          <t>assay [obi]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>dataset creating</t>
+          <t>completely executed planned process</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Elisabetta Manduchi</t>
+          <t>PlanAndPlannedProcess Branch</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>A k-means clustering is a data transformation which achieves a class discovery or partitioning objective, which takes as input a collection of objects (represented as points in multidimensional space) and which partitions them into a specified number k of clusters. The algorithm attempts to find the centers of natural clusters in the data. The most common form of the algorithm starts by partitioning the input points into k initial sets, either at random or using some heuristic data. It then calculates the mean point, or centroid, of each set. It constructs a new partition by associating each point with the closest centroid. Then the centroids are recalculated for the new clusters, and the algorithm repeated by alternate applications of these two steps until convergence, which is obtained when the points no longer switch clusters (or alternatively centroids are no longer changed).</t>
+          <t>A planned process with the objective to produce information about the material entity that is the evaluant, by physically examining it or its proxies.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -538,22 +538,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>hierarchical clustering [obi]</t>
+          <t>principal components analysis dimensionality reduction [obi]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>class discovery data transformation</t>
+          <t>dimensionality reduction</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>James Malone</t>
+          <t>Philippe Rocca-Serra</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>A hierarchical clustering is a data transformation which achieves a class discovery objective, which takes as input data item and builds a hierarchy of clusters. The traditional representation of this hierarchy is a tree (visualized by a dendrogram), with the individual input objects at one end (leaves) and a single cluster containing every object at the other (root).</t>
+          <t>A principal components analysis dimensionality reduction is a dimensionality reduction achieved by applying principal components analysis and by keeping low-order principal components and excluding higher-order ones.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -584,22 +584,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>manufacturing [obi]</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>material processing [obi]</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>planned process</t>
-        </is>
-      </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>PERSON: Frank Gibson</t>
+          <t>PERSON: Philippe Rocca-Serra</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>A planned process which results in physical changes in a specified input material</t>
+          <t>Manufacturing is a process with the intent to produce a processed material which will have a function for future use. A person or organization (having manufacturer role) is a participant in this process</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -607,22 +607,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>protocol [obi]</t>
+          <t>class prediction data transformation [obi]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>plan specification</t>
+          <t>data transformation</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>PlanAndPlannedProcess Branch</t>
+          <t>James Malone</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>A plan specification which has sufficient level of detail and quantitative information to communicate it between investigation agents, so that different investigation agents will reliably be able to independently reproduce the process.</t>
+          <t>A class prediction data transformation (sometimes called supervised classification) is a data transformation that has objective class prediction.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -630,22 +630,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>processed material [obi]</t>
+          <t>k-means clustering [obi]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>material entity</t>
+          <t>dataset creating</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>PERSON: Alan Ruttenberg</t>
+          <t>Elisabetta Manduchi</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Is a material entity that is created or changed during material processing.</t>
+          <t>A k-means clustering is a data transformation which achieves a class discovery or partitioning objective, which takes as input a collection of objects (represented as points in multidimensional space) and which partitions them into a specified number k of clusters. The algorithm attempts to find the centers of natural clusters in the data. The most common form of the algorithm starts by partitioning the input points into k initial sets, either at random or using some heuristic data. It then calculates the mean point, or centroid, of each set. It constructs a new partition by associating each point with the closest centroid. Then the centroids are recalculated for the new clusters, and the algorithm repeated by alternate applications of these two steps until convergence, which is obtained when the points no longer switch clusters (or alternatively centroids are no longer changed).</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
@@ -653,22 +653,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>processed specimen [obi]</t>
+          <t>hierarchical clustering [obi]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>processed material [obi]</t>
+          <t>dataset creating</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bjoern Peters</t>
+          <t>James Malone</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>A specimen that has been intentionally physically modified.</t>
+          <t>A hierarchical clustering is a data transformation which achieves a class discovery objective, which takes as input data item and builds a hierarchy of clusters. The traditional representation of this hierarchy is a tree (visualized by a dendrogram), with the individual input objects at one end (leaves) and a single cluster containing every object at the other (root).</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -676,22 +676,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>principal components analysis dimensionality reduction [obi]</t>
+          <t>processed specimen [obi]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>dimensionality reduction</t>
+          <t>specimen [obi]</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Philippe Rocca-Serra</t>
+          <t>Bjoern Peters</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>A principal components analysis dimensionality reduction is a dimensionality reduction achieved by applying principal components analysis and by keeping low-order principal components and excluding higher-order ones.</t>
+          <t>A specimen that has been intentionally physically modified.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -699,25 +699,48 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>class prediction data transformation [obi]</t>
+          <t>material processing [obi]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>data transformation</t>
+          <t>planned process</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>PERSON: Jennifer Fostel</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>A planned process which results in physical changes in a specified input material</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>k-nearest neighbors [obi]</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>dataset creating</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
           <t>James Malone</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>A class prediction data transformation (sometimes called supervised classification) is a data transformation that has objective class prediction.</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>A k-nearest neighbors is a data transformation which achieves a class discovery or partitioning objective, in which an input data object with vector y is assigned to a class label based upon the k closest training data set points to y; where k is the largest value that class label is assigned.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
